--- a/data/PRO.xlsx
+++ b/data/PRO.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\SABAA PROJECT SHORT SCREEN\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01BDA9A-B09F-4879-A3F5-2C97D706A95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{003A1A0D-2907-4124-8064-EFAA1CE764D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,9 +41,6 @@
     <t>Emirates ID No</t>
   </si>
   <si>
-    <t>Date Of Bairh</t>
-  </si>
-  <si>
     <t>Mobile Number</t>
   </si>
   <si>
@@ -123,13 +114,16 @@
   </si>
   <si>
     <t>PRO Name Ar</t>
+  </si>
+  <si>
+    <t>Date Of Birth</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,7 +231,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -289,7 +283,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -503,41 +497,41 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5451B0F4-B33B-49E5-BC50-6E71ED632D18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -546,367 +540,367 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
       </c>
       <c r="D2">
         <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" s="4">
         <v>31103</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2">
         <v>63524121</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
       </c>
       <c r="D3">
         <v>119</v>
       </c>
       <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="G3" s="4">
         <v>27404</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3">
         <v>69511411</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
       </c>
       <c r="D4">
         <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4">
         <v>31103</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4">
         <v>63524121</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
       </c>
       <c r="D5">
         <v>119</v>
       </c>
       <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="G5" s="4">
         <v>27404</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5">
         <v>69511411</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13">
       <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
       </c>
       <c r="D6">
         <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" s="4">
         <v>31103</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>63524121</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
       </c>
       <c r="D7">
         <v>119</v>
       </c>
       <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="G7" s="4">
         <v>27404</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7">
         <v>69511411</v>
       </c>
       <c r="J7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13">
       <c r="A8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
       </c>
       <c r="D8">
         <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" s="4">
         <v>31103</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I8">
         <v>63524121</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
       </c>
       <c r="D9">
         <v>119</v>
       </c>
       <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="G9" s="4">
         <v>27404</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9">
         <v>69511411</v>
       </c>
       <c r="J9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="A10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
       </c>
       <c r="D10">
         <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G10" s="4">
         <v>31103</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I10">
         <v>63524121</v>
       </c>
       <c r="J10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
